--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D4420E-925E-4407-89F2-4789DAABDA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C48C3B-6A68-4046-9C02-321A09C5927F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="649">
   <si>
     <t>Id</t>
   </si>
@@ -1995,10 +1995,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>CCB隐身</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>CCB减攻速,减速</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2397,10 +2393,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>CCB普攻,获得点赞,获得投币,获得收藏</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>干员</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -2413,6 +2405,10 @@
   </si>
   <si>
     <t>agoat2_skill_03_buff_01</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2915,10 +2911,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -3575,19 +3571,19 @@
     </row>
     <row r="5" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3630,25 +3626,25 @@
         <v>1</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AK5" t="s">
         <v>136</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AN5" s="2" t="s">
         <v>473</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AQ5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AR5">
         <v>2</v>
@@ -3660,10 +3656,10 @@
         <v>0.25</v>
       </c>
       <c r="BE5" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="BF5" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>618</v>
       </c>
       <c r="BG5" s="1" t="str">
         <f t="shared" ref="BG5" si="0">"icon_"&amp;D5</f>
@@ -3713,7 +3709,7 @@
         <v>135</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM6" s="2"/>
     </row>
@@ -3768,16 +3764,16 @@
         <v>136</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN7" s="3" t="s">
         <v>501</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AP7" s="1">
         <v>1</v>
@@ -3820,13 +3816,13 @@
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B9" t="s">
         <v>557</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>558</v>
-      </c>
-      <c r="F9" t="s">
-        <v>559</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -3871,20 +3867,20 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AK9" t="s">
         <v>136</v>
       </c>
       <c r="AL9" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="AM9" t="s">
         <v>574</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>575</v>
       </c>
       <c r="AO9" s="1"/>
       <c r="AQ9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3899,23 +3895,23 @@
         <v>0.25</v>
       </c>
       <c r="BE9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:76" x14ac:dyDescent="0.25">
       <c r="E10" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>515</v>
@@ -3961,16 +3957,16 @@
         <v>136</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN11" s="3" t="s">
         <v>501</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AP11" s="1">
         <v>1</v>
@@ -3985,7 +3981,7 @@
         <v>0.25</v>
       </c>
       <c r="BG11" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="BM11" s="1" t="s">
         <v>497</v>
@@ -4012,10 +4008,10 @@
     </row>
     <row r="12" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>515</v>
@@ -4061,16 +4057,16 @@
         <v>136</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN12" s="3" t="s">
         <v>501</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AP12" s="1">
         <v>1</v>
@@ -4085,7 +4081,7 @@
         <v>0.25</v>
       </c>
       <c r="BG12" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="BM12" s="1" t="s">
         <v>497</v>
@@ -4112,10 +4108,10 @@
     </row>
     <row r="13" spans="1:76" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>515</v>
@@ -4161,16 +4157,16 @@
         <v>136</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN13" s="3" t="s">
         <v>501</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AP13" s="1">
         <v>1</v>
@@ -4185,7 +4181,7 @@
         <v>0.25</v>
       </c>
       <c r="BG13" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="BM13" s="1" t="s">
         <v>497</v>
@@ -4779,7 +4775,7 @@
         <v>290</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AW2" t="s">
         <v>291</v>
@@ -4896,7 +4892,7 @@
         <v>326</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="CJ2" t="s">
         <v>327</v>
@@ -5325,13 +5321,13 @@
         <v>371</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K6" t="s">
         <v>373</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AC6">
         <v>2</v>
@@ -5343,7 +5339,7 @@
         <v>374</v>
       </c>
       <c r="AT6" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AX6" t="s">
         <v>375</v>
@@ -5361,22 +5357,22 @@
         <v>0.25</v>
       </c>
       <c r="BP6" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="BQ6" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="CB6" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="CG6" t="s">
         <v>376</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="CI6" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="CJ6" s="2" t="s">
         <v>531</v>
@@ -5388,7 +5384,7 @@
         <v>12</v>
       </c>
       <c r="CU6" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="CY6" t="s">
         <v>379</v>
@@ -5426,7 +5422,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AV7">
         <v>16</v>
@@ -5684,9 +5680,7 @@
       <c r="K16" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="O16" s="2" t="s">
-        <v>540</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="AC16">
         <v>2</v>
       </c>
@@ -5716,7 +5710,7 @@
         <v>522</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CO16">
         <v>-50</v>
@@ -5728,7 +5722,7 @@
         <v>3</v>
       </c>
       <c r="CU16" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
@@ -5740,10 +5734,10 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>506</v>
@@ -5762,7 +5756,7 @@
       </c>
       <c r="BY17" s="2"/>
       <c r="CU17" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
@@ -5811,13 +5805,13 @@
         <v>378</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="CO18">
         <v>-0.8</v>
       </c>
       <c r="CU18" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="CY18" t="s">
         <v>379</v>
@@ -5872,7 +5866,7 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>475</v>
@@ -5893,7 +5887,7 @@
         <v>482</v>
       </c>
       <c r="AX20" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AZ20">
         <v>0.05</v>
@@ -5908,7 +5902,7 @@
         <v>0.5</v>
       </c>
       <c r="CY20" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -5922,16 +5916,16 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>481</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -5952,25 +5946,25 @@
         <v>1</v>
       </c>
       <c r="BY22" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="CU22" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -5979,7 +5973,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AN23">
         <v>1</v>
@@ -5989,7 +5983,7 @@
       </c>
       <c r="BY23" s="2"/>
       <c r="CN23" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="CR23">
         <v>10</v>
@@ -6000,17 +5994,17 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -6028,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="AX25" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AZ25">
         <v>1.5</v>
@@ -6043,7 +6037,7 @@
         <v>0.04</v>
       </c>
       <c r="BP25" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="BT25">
         <v>2.5</v>
@@ -6058,55 +6052,55 @@
         <v>1</v>
       </c>
       <c r="BY25" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="CB25" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="CE25" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="CF25" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="CG25" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="CH25" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="CI25" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="CE25" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="CF25" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="CG25" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="CH25" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="CI25" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="CJ25" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="CU25" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="CY25" s="2"/>
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="BD26">
         <v>1</v>
       </c>
       <c r="CN26" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="CR26">
         <v>3</v>
@@ -6114,25 +6108,25 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K28" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>601</v>
-      </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="BT28">
         <v>2.5</v>
@@ -6147,21 +6141,21 @@
         <v>1</v>
       </c>
       <c r="BY28" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C31" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>381</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -6198,21 +6192,21 @@
       <c r="CA31" s="8"/>
       <c r="CN31" s="9"/>
       <c r="CU31" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C32" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>381</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -6249,21 +6243,21 @@
       <c r="CA32" s="8"/>
       <c r="CN32" s="9"/>
       <c r="CU32" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="33" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C33" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>381</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -6300,7 +6294,7 @@
       <c r="CA33" s="8"/>
       <c r="CN33" s="9"/>
       <c r="CU33" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="684" spans="90:90" x14ac:dyDescent="0.25">
@@ -6583,7 +6577,7 @@
         <v>511</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>512</v>
@@ -6616,16 +6610,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="K11">
         <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -6644,24 +6638,24 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J16" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -6836,7 +6830,7 @@
         <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6863,6 +6857,9 @@
       <c r="B6" s="2" t="s">
         <v>519</v>
       </c>
+      <c r="C6" t="s">
+        <v>521</v>
+      </c>
       <c r="E6">
         <v>10</v>
       </c>
@@ -6872,13 +6869,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>519</v>
       </c>
       <c r="C7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E7">
         <v>2.25</v>
@@ -6887,18 +6884,18 @@
         <v>2</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>519</v>
       </c>
       <c r="C8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -6907,17 +6904,12 @@
         <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>521</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -7056,10 +7048,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K5">
         <v>60</v>
@@ -7070,10 +7062,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B7" t="s">
         <v>613</v>
-      </c>
-      <c r="B7" t="s">
-        <v>614</v>
       </c>
       <c r="K7">
         <v>60</v>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4542B5EE-12C4-4168-A06C-CCCDF7F389D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E1080-FECB-4A98-989C-9D760D1DFA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="617">
   <si>
     <t>Id</t>
   </si>
@@ -1577,9 +1577,6 @@
   </si>
   <si>
     <t>Normal</t>
-  </si>
-  <si>
-    <t>电大</t>
   </si>
   <si>
     <t>1,4</t>
@@ -2179,6 +2176,10 @@
   </si>
   <si>
     <t>{"Expression":"Target.MainSkill.Power = Target.MainSkill.Power - 1f / 60 * (Target.MainSkill.Power &lt; 1f / 60 ? 0 : 2)","绑定进度条":"圆"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>电大</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2267,7 +2268,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2287,6 +2288,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3339,7 +3343,7 @@
         <v>140</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AM5" s="3" t="s">
         <v>142</v>
@@ -3416,7 +3420,7 @@
         <v>155</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AM6" s="3"/>
     </row>
@@ -5069,35 +5073,38 @@
       <c r="BF6" s="1">
         <v>0.25</v>
       </c>
+      <c r="BP6" s="7" t="s">
+        <v>616</v>
+      </c>
       <c r="BQ6" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="CB6" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="CB6" s="1" t="s">
+      <c r="CH6" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="CH6" s="1" t="s">
+      <c r="CI6" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="CI6" s="1" t="s">
+      <c r="CJ6" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="CJ6" s="1" t="s">
+      <c r="CK6" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="CK6" s="1" t="s">
+      <c r="CO6" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="CO6" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="CS6" s="1">
         <v>12</v>
       </c>
       <c r="CV6" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="CZ6" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="CZ6" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="DE6" s="1">
         <v>1</v>
@@ -5111,19 +5118,19 @@
     </row>
     <row r="7" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="AC7" s="1">
         <v>2</v>
@@ -5141,27 +5148,27 @@
         <v>99</v>
       </c>
       <c r="CI7" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="K8" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AX8" s="1" t="s">
         <v>417</v>
@@ -5176,30 +5183,30 @@
         <v>1</v>
       </c>
       <c r="CM8" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="CZ8" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="CZ8" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AC10" s="1">
         <v>1</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BD10" s="1">
         <v>1</v>
@@ -5217,21 +5224,21 @@
         <v>1</v>
       </c>
       <c r="BY10" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="CO10" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>413</v>
@@ -5267,42 +5274,42 @@
         <v>1</v>
       </c>
       <c r="BY12" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="CB12" s="1" t="s">
         <v>62</v>
       </c>
       <c r="CH12" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CI12" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="CJ12" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="CJ12" s="1" t="s">
+      <c r="CK12" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="CK12" s="1" t="s">
+      <c r="CO12" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="CV12" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="CO12" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="CV12" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="CZ12" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>413</v>
@@ -5311,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BD13" s="1">
         <v>1</v>
@@ -5332,7 +5339,7 @@
         <v>413</v>
       </c>
       <c r="CO13" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="CP13" s="1">
         <v>200</v>
@@ -5346,13 +5353,13 @@
     </row>
     <row r="14" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>413</v>
@@ -5361,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BD14" s="1">
         <v>1</v>
@@ -5379,21 +5386,21 @@
         <v>1</v>
       </c>
       <c r="BY14" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="CO14" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="CV14" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="CV14" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>413</v>
@@ -5402,16 +5409,16 @@
         <v>2</v>
       </c>
       <c r="AO16" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="AR16" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="AR16" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="AV16" s="1">
         <v>8</v>
       </c>
       <c r="AX16" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AZ16" s="1">
         <v>1.5</v>
@@ -5423,10 +5430,10 @@
         <v>6</v>
       </c>
       <c r="CI16" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="CO16" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="CO16" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="CP16" s="1">
         <v>-50</v>
@@ -5438,24 +5445,24 @@
         <v>3</v>
       </c>
       <c r="CV16" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="Q17" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5467,15 +5474,15 @@
         <v>1</v>
       </c>
       <c r="CV17" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>413</v>
@@ -5487,7 +5494,7 @@
         <v>415</v>
       </c>
       <c r="AR18" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AV18" s="1">
         <v>3.5</v>
@@ -5505,25 +5512,25 @@
         <v>62</v>
       </c>
       <c r="CH18" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CI18" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="CJ18" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="CO18" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="CP18" s="1">
         <v>-0.8</v>
       </c>
       <c r="CV18" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="CZ18" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:113" x14ac:dyDescent="0.25">
@@ -5531,10 +5538,10 @@
         <v>160</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>413</v>
@@ -5543,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
@@ -5564,7 +5571,7 @@
         <v>413</v>
       </c>
       <c r="CO19" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="CP19" s="1">
         <v>100</v>
@@ -5575,10 +5582,10 @@
     </row>
     <row r="20" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
@@ -5593,10 +5600,10 @@
         <v>1</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AX20" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AZ20" s="1">
         <v>0.05</v>
@@ -5611,7 +5618,7 @@
         <v>0.5</v>
       </c>
       <c r="CZ20" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="DE20" s="1">
         <v>1</v>
@@ -5625,16 +5632,16 @@
     </row>
     <row r="22" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="J22" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="X22" s="1">
         <v>1</v>
@@ -5658,7 +5665,7 @@
         <v>413</v>
       </c>
       <c r="CV22" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:113" x14ac:dyDescent="0.25">
@@ -5666,13 +5673,13 @@
         <v>170</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AC23" s="1">
         <v>7</v>
@@ -5681,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN23" s="1">
         <v>1</v>
@@ -5700,17 +5707,17 @@
       </c>
     </row>
     <row r="25" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>418</v>
+      <c r="A25" s="6" t="s">
+        <v>616</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>412</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="X25" s="1">
         <v>1</v>
@@ -5743,7 +5750,7 @@
         <v>0.04</v>
       </c>
       <c r="BP25" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="BT25" s="1">
         <v>2.5</v>
@@ -5758,48 +5765,48 @@
         <v>1</v>
       </c>
       <c r="BY25" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="CB25" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="CB25" s="1" t="s">
+      <c r="CF25" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="CG25" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="CH25" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="CI25" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="CF25" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="CG25" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="CH25" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="CI25" s="1" t="s">
+      <c r="CJ25" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="CJ25" s="1" t="s">
+      <c r="CK25" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="CV25" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="CK25" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="CV25" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC26" s="1">
         <v>1</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BD26" s="1">
         <v>1</v>
@@ -5816,13 +5823,13 @@
         <v>142</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>414</v>
@@ -5831,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BT28" s="1">
         <v>2.5</v>
@@ -5851,89 +5858,89 @@
     </row>
     <row r="31" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="K31" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="L31" s="1" t="s">
+      <c r="AC31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="BD31" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV31" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="BD31" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV31" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="32" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="BD32" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV32" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="AC32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="BD32" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV32" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="33" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="BD33" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV33" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="AC33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="BD33" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV33" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="684" spans="91:91" x14ac:dyDescent="0.25">
@@ -5996,7 +6003,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -6019,37 +6026,37 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -6063,40 +6070,40 @@
         <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>379</v>
@@ -6154,55 +6161,55 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K4" s="1">
         <v>5</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K6" s="1">
         <v>99999</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>522</v>
       </c>
       <c r="K7" s="1">
         <v>12</v>
@@ -6210,69 +6217,69 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="J8" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="Q10" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K11" s="1">
         <v>0.8</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="J12" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -6280,10 +6287,10 @@
         <v>165</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -6291,10 +6298,15 @@
         <v>414</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
+      </c>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="3" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -6320,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6331,7 +6343,7 @@
         <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>379</v>
@@ -6353,16 +6365,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -6402,19 +6414,19 @@
         <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>545</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>368</v>
@@ -6457,64 +6469,64 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="E4" s="1">
         <v>4</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="E5" s="1">
         <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>554</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E7" s="1">
         <v>2.25</v>
@@ -6523,18 +6535,18 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -6543,12 +6555,12 @@
         <v>2</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -6576,34 +6588,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -6611,34 +6623,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>579</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>104</v>
@@ -6687,10 +6699,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K5" s="1">
         <v>60</v>
@@ -6701,10 +6713,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>582</v>
       </c>
       <c r="K7" s="1">
         <v>60</v>
@@ -6744,22 +6756,22 @@
         <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>584</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>316</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>59</v>
@@ -6788,7 +6800,7 @@
         <v>128</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>128</v>
@@ -6824,28 +6836,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6853,28 +6865,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6908,28 +6920,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E1080-FECB-4A98-989C-9D760D1DFA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469F9B7B-E1DD-4EE8-8D46-9073ABAD34A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="620">
   <si>
     <t>Id</t>
   </si>
@@ -2180,6 +2180,17 @@
   </si>
   <si>
     <t>电大</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>洁哥2抬手</t>
+  </si>
+  <si>
+    <t>aglina_skill_03_start_summer#5</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>myrtle_attack_01_start_taiko#1</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2268,7 +2279,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2288,9 +2299,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5073,7 +5081,7 @@
       <c r="BF6" s="1">
         <v>0.25</v>
       </c>
-      <c r="BP6" s="7" t="s">
+      <c r="BP6" s="1" t="s">
         <v>616</v>
       </c>
       <c r="BQ6" s="1" t="s">
@@ -6003,7 +6011,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -6300,13 +6308,13 @@
       <c r="C16" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="3" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J18" s="3" t="s">
-        <v>524</v>
+    <row r="17" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="1" t="s">
+        <v>617</v>
       </c>
     </row>
   </sheetData>
@@ -6572,7 +6580,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
@@ -6701,8 +6709,8 @@
       <c r="A5" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>579</v>
+      <c r="B5" s="6" t="s">
+        <v>619</v>
       </c>
       <c r="K5" s="1">
         <v>60</v>
@@ -6720,6 +6728,16 @@
       </c>
       <c r="K7" s="1">
         <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469F9B7B-E1DD-4EE8-8D46-9073ABAD34A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02739AC-462A-4AAA-A63F-92411464B789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="621">
   <si>
     <t>Id</t>
   </si>
@@ -2191,6 +2191,10 @@
   </si>
   <si>
     <t>myrtle_attack_01_start_taiko#1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>agoat2_skill_03_buff_01</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -6580,7 +6584,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
@@ -6709,8 +6713,8 @@
       <c r="A5" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>619</v>
+      <c r="B5" s="5" t="s">
+        <v>620</v>
       </c>
       <c r="K5" s="1">
         <v>60</v>
@@ -6738,6 +6742,11 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>618</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>619</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02739AC-462A-4AAA-A63F-92411464B789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7630D4E8-C207-4A35-915F-6C51545A993F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="622">
   <si>
     <t>Id</t>
   </si>
@@ -2196,6 +2196,9 @@
   <si>
     <t>agoat2_skill_03_buff_01</t>
     <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌尔比安3爆炸</t>
   </si>
 </sst>
 </file>
@@ -6015,7 +6018,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -6312,13 +6315,18 @@
       <c r="C16" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>524</v>
+      <c r="J16" s="1" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J17" s="1" t="s">
         <v>617</v>
+      </c>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="3" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7630D4E8-C207-4A35-915F-6C51545A993F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7B46E9-4DC6-4A6F-8608-31CCDB140BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="621">
   <si>
     <t>Id</t>
   </si>
@@ -736,15 +736,6 @@
     <t>干员</t>
   </si>
   <si>
-    <t>thorns</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>char_1039_thorn2</t>
-  </si>
-  <si>
     <t>Hip</t>
   </si>
   <si>
@@ -1580,9 +1571,6 @@
   </si>
   <si>
     <t>1,4</t>
-  </si>
-  <si>
-    <t>Skill_2</t>
   </si>
   <si>
     <t>跟随攻击</t>
@@ -2199,6 +2187,18 @@
   </si>
   <si>
     <t>乌尔比安3爆炸</t>
+  </si>
+  <si>
+    <t>clemnt</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>char_4231_clemnt</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2_Loop</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3303,13 +3303,13 @@
         <v>136</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>138</v>
+        <v>618</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4231</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>139</v>
+        <v>619</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -3355,22 +3355,22 @@
         <v>4</v>
       </c>
       <c r="AK5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL5" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="AM5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN5" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="AL5" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="AM5" s="3" t="s">
+      <c r="AO5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="AN5" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO5" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="AR5" s="1">
         <v>2</v>
@@ -3382,49 +3382,49 @@
         <v>0.25</v>
       </c>
       <c r="BE5" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="BG5" s="2" t="str">
         <f>"icon_"&amp;D5</f>
-        <v>icon_thorns</v>
+        <v>icon_clemnt</v>
       </c>
       <c r="BH5" s="2" t="str">
         <f>"half_"&amp;D5</f>
-        <v>half_thorns</v>
+        <v>half_clemnt</v>
       </c>
       <c r="BI5" s="2" t="str">
         <f>D5</f>
-        <v>thorns</v>
+        <v>clemnt</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="BK5" s="1">
         <v>6</v>
       </c>
       <c r="BL5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BM5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="BQ5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BR5" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="BM5" s="1" t="s">
+      <c r="BT5" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="BQ5" s="1" t="s">
+      <c r="BU5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="BV5" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="BR5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BT5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BU5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BV5" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="BX5" s="1">
         <v>1</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="6" spans="1:76" x14ac:dyDescent="0.25">
       <c r="F6" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="AM6" s="3"/>
     </row>
     <row r="7" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E7" s="2">
         <v>1150</v>
@@ -3484,22 +3484,22 @@
         <v>0.75</v>
       </c>
       <c r="AJ7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL7" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AK7" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="AM7" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AN7" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AP7" s="2">
         <v>1</v>
@@ -3518,22 +3518,22 @@
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="BN7" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="BQ7" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="BR7" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="BS7" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="BT7" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="BX7" s="2">
         <v>1</v>
@@ -3541,13 +3541,13 @@
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G9" s="1">
         <v>10</v>
@@ -3592,20 +3592,20 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AL9" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AM9" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AO9" s="2"/>
       <c r="AQ9" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AR9" s="1">
         <v>0</v>
@@ -3620,32 +3620,32 @@
         <v>0.25</v>
       </c>
       <c r="BE9" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="BO9" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:76" x14ac:dyDescent="0.25">
       <c r="E10" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>136</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E11" s="2">
         <v>1150</v>
       </c>
       <c r="F11" s="2" t="str">
-        <f t="shared" ref="F11:F13" si="0">"enemy_"&amp;E11&amp;"_"&amp;D11</f>
+        <f>"enemy_"&amp;E11&amp;"_"&amp;D11</f>
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="G11" s="2">
@@ -3676,22 +3676,22 @@
         <v>0.75</v>
       </c>
       <c r="AJ11" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL11" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AK11" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL11" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="AM11" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AN11" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AP11" s="2">
         <v>1</v>
@@ -3706,25 +3706,25 @@
         <v>0.25</v>
       </c>
       <c r="BG11" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="BM11" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="BN11" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="BQ11" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="BR11" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="BS11" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="BT11" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="BX11" s="2">
         <v>1</v>
@@ -3732,19 +3732,19 @@
     </row>
     <row r="12" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>136</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2">
         <v>1150</v>
       </c>
       <c r="F12" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F12:F13" si="0">"enemy_"&amp;E12&amp;"_"&amp;D12</f>
         <v>enemy_1150_dsjely</v>
       </c>
       <c r="G12" s="2">
@@ -3775,22 +3775,22 @@
         <v>0.75</v>
       </c>
       <c r="AJ12" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL12" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AK12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL12" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="AM12" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AN12" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AO12" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AP12" s="2">
         <v>1</v>
@@ -3805,25 +3805,25 @@
         <v>0.25</v>
       </c>
       <c r="BG12" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="BM12" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="BN12" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="BQ12" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="BR12" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="BS12" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="BT12" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="BX12" s="2">
         <v>1</v>
@@ -3831,13 +3831,13 @@
     </row>
     <row r="13" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>136</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E13" s="2">
         <v>1150</v>
@@ -3874,22 +3874,22 @@
         <v>0.75</v>
       </c>
       <c r="AJ13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL13" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AK13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL13" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="AM13" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AN13" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AO13" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AP13" s="2">
         <v>1</v>
@@ -3904,25 +3904,25 @@
         <v>0.25</v>
       </c>
       <c r="BG13" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="BM13" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="BN13" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="BQ13" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="BR13" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="BS13" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="BT13" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="BX13" s="2">
         <v>1</v>
@@ -4028,337 +4028,337 @@
   <sheetData>
     <row r="1" spans="1:114" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="BJ1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="CT1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="CS1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="DB1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="DA1" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="DH1" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="DJ1" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:114" x14ac:dyDescent="0.25">
@@ -4372,334 +4372,334 @@
         <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="BO2" s="1" t="s">
         <v>86</v>
       </c>
       <c r="BP2" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="BS2" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BT2" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="BR2" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="BT2" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="BU2" s="1" t="s">
         <v>102</v>
       </c>
       <c r="BV2" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="BW2" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="BX2" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="BY2" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BZ2" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="BX2" s="1" t="s">
+      <c r="CA2" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="CE2" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="CH2" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="CK2" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="CN2" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="CL2" s="1" t="s">
+      <c r="CO2" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="CM2" s="1" t="s">
+      <c r="CP2" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="CN2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="CR2" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="CP2" s="1" t="s">
+      <c r="CS2" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="CQ2" s="1" t="s">
+      <c r="CT2" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="CR2" s="1" t="s">
+      <c r="CU2" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="CS2" s="1" t="s">
+      <c r="CV2" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="CT2" s="1" t="s">
+      <c r="CW2" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="CU2" s="1" t="s">
+      <c r="CX2" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="CV2" s="1" t="s">
+      <c r="CY2" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="CW2" s="1" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="CX2" s="1" t="s">
+      <c r="DA2" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="CY2" s="1" t="s">
+      <c r="DB2" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="CZ2" s="1" t="s">
+      <c r="DC2" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="DA2" s="1" t="s">
+      <c r="DD2" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="DB2" s="1" t="s">
+      <c r="DE2" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="DC2" s="1" t="s">
+      <c r="DF2" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="DD2" s="1" t="s">
+      <c r="DG2" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="DE2" s="1" t="s">
+      <c r="DH2" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="DF2" s="1" t="s">
+      <c r="DI2" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="DG2" s="1" t="s">
+      <c r="DJ2" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="DH2" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="DI2" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="DJ2" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:114" x14ac:dyDescent="0.25">
@@ -4728,13 +4728,13 @@
         <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>128</v>
@@ -4797,7 +4797,7 @@
         <v>125</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AH3" s="1" t="s">
         <v>125</v>
@@ -4821,10 +4821,10 @@
         <v>125</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4836,7 +4836,7 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AU3" s="1" t="s">
         <v>125</v>
@@ -4848,7 +4848,7 @@
         <v>125</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AY3" s="1" t="s">
         <v>125</v>
@@ -4878,7 +4878,7 @@
         <v>125</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="BI3" s="1" t="s">
         <v>125</v>
@@ -4905,10 +4905,10 @@
         <v>129</v>
       </c>
       <c r="BQ3" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="BR3" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="BS3" s="1" t="s">
         <v>126</v>
@@ -4929,13 +4929,13 @@
         <v>128</v>
       </c>
       <c r="BY3" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="BZ3" s="1" t="s">
         <v>125</v>
       </c>
       <c r="CA3" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="CB3" s="1" t="s">
         <v>130</v>
@@ -4944,7 +4944,7 @@
         <v>125</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="CE3" s="1" t="s">
         <v>130</v>
@@ -4956,19 +4956,19 @@
         <v>130</v>
       </c>
       <c r="CH3" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="CI3" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="CJ3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="CK3" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="CL3" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="CM3" s="1" t="s">
         <v>135</v>
@@ -4989,7 +4989,7 @@
         <v>134</v>
       </c>
       <c r="CS3" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="CT3" s="1" t="s">
         <v>134</v>
@@ -5001,28 +5001,28 @@
         <v>135</v>
       </c>
       <c r="CW3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="CX3" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="CY3" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="CZ3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="DC3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="DE3" s="1" t="s">
         <v>125</v>
@@ -5045,21 +5045,21 @@
     </row>
     <row r="4" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AC6" s="1">
         <v>2</v>
@@ -5068,13 +5068,13 @@
         <v>1</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AT6" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AX6" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AZ6" s="1">
         <v>1</v>
@@ -5089,37 +5089,37 @@
         <v>0.25</v>
       </c>
       <c r="BP6" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="BQ6" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="CB6" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="CH6" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="CI6" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="CJ6" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="CB6" s="1" t="s">
+      <c r="CK6" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="CH6" s="1" t="s">
+      <c r="CO6" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="CI6" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="CJ6" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="CK6" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="CO6" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="CS6" s="1">
         <v>12</v>
       </c>
       <c r="CV6" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="CZ6" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="DE6" s="1">
         <v>1</v>
@@ -5133,19 +5133,19 @@
     </row>
     <row r="7" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="AC7" s="1">
         <v>2</v>
@@ -5154,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AV7" s="1">
         <v>16</v>
@@ -5163,30 +5163,30 @@
         <v>99</v>
       </c>
       <c r="CI7" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AZ8" s="1">
         <v>0</v>
@@ -5198,30 +5198,30 @@
         <v>1</v>
       </c>
       <c r="CM8" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="CZ8" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="AC10" s="1">
         <v>1</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BD10" s="1">
         <v>1</v>
@@ -5239,36 +5239,36 @@
         <v>1</v>
       </c>
       <c r="BY10" s="6" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="CO10" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AV12" s="1">
         <v>8</v>
       </c>
       <c r="AX12" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AZ12" s="1">
         <v>2.5</v>
@@ -5289,51 +5289,51 @@
         <v>1</v>
       </c>
       <c r="BY12" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="CB12" s="1" t="s">
         <v>62</v>
       </c>
       <c r="CH12" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="CI12" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="CJ12" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="CK12" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="CO12" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="CV12" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="CZ12" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AC13" s="1">
         <v>1</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BD13" s="1">
         <v>1</v>
@@ -5351,10 +5351,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="CO13" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="CP13" s="1">
         <v>200</v>
@@ -5368,22 +5368,22 @@
     </row>
     <row r="14" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AC14" s="1">
         <v>1</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BD14" s="1">
         <v>1</v>
@@ -5401,39 +5401,39 @@
         <v>1</v>
       </c>
       <c r="BY14" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="CO14" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="CV14" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AC16" s="1">
         <v>2</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="AR16" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AV16" s="1">
         <v>8</v>
       </c>
       <c r="AX16" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AZ16" s="1">
         <v>1.5</v>
@@ -5445,10 +5445,10 @@
         <v>6</v>
       </c>
       <c r="CI16" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="CO16" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="CP16" s="1">
         <v>-50</v>
@@ -5460,24 +5460,24 @@
         <v>3</v>
       </c>
       <c r="CV16" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5489,33 +5489,33 @@
         <v>1</v>
       </c>
       <c r="CV17" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AC18" s="1">
         <v>2</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AR18" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AV18" s="1">
         <v>3.5</v>
       </c>
       <c r="AX18" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AZ18" s="1">
         <v>1</v>
@@ -5527,45 +5527,45 @@
         <v>62</v>
       </c>
       <c r="CH18" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="CI18" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="CJ18" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="CO18" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="CP18" s="1">
         <v>-0.8</v>
       </c>
       <c r="CV18" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="CZ18" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
@@ -5583,10 +5583,10 @@
         <v>1</v>
       </c>
       <c r="BY19" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="CO19" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="CP19" s="1">
         <v>100</v>
@@ -5597,16 +5597,16 @@
     </row>
     <row r="20" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AC20" s="1">
         <v>1</v>
@@ -5615,10 +5615,10 @@
         <v>1</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AX20" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="AZ20" s="1">
         <v>0.05</v>
@@ -5633,7 +5633,7 @@
         <v>0.5</v>
       </c>
       <c r="CZ20" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="DE20" s="1">
         <v>1</v>
@@ -5647,16 +5647,16 @@
     </row>
     <row r="22" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="X22" s="1">
         <v>1</v>
@@ -5677,24 +5677,24 @@
         <v>1</v>
       </c>
       <c r="BY22" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="CV22" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="AC23" s="1">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AN23" s="1">
         <v>1</v>
@@ -5712,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="CO23" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="CS23" s="1">
         <v>10</v>
@@ -5723,16 +5723,16 @@
     </row>
     <row r="25" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="X25" s="1">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>1</v>
       </c>
       <c r="AX25" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AZ25" s="1">
         <v>1.5</v>
@@ -5765,7 +5765,7 @@
         <v>0.04</v>
       </c>
       <c r="BP25" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="BT25" s="1">
         <v>2.5</v>
@@ -5780,54 +5780,54 @@
         <v>1</v>
       </c>
       <c r="BY25" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="CB25" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="CF25" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="CG25" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="CH25" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="CI25" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="CJ25" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="CK25" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="CV25" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="CB25" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="CF25" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="CG25" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="CH25" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="CI25" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="CJ25" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="CK25" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="CV25" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AC26" s="1">
         <v>1</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BD26" s="1">
         <v>1</v>
       </c>
       <c r="CO26" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="CS26" s="1">
         <v>3</v>
@@ -5835,25 +5835,25 @@
     </row>
     <row r="28" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BT28" s="1">
         <v>2.5</v>
@@ -5868,21 +5868,21 @@
         <v>1</v>
       </c>
       <c r="BY28" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="31" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="AC31" s="1">
         <v>1</v>
@@ -5891,56 +5891,56 @@
         <v>1</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BD31" s="1">
         <v>1</v>
       </c>
       <c r="CV31" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD32" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV32" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="AC32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="BD32" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV32" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="AC33" s="1">
         <v>1</v>
@@ -5949,13 +5949,13 @@
         <v>1</v>
       </c>
       <c r="AG33" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BD33" s="1">
         <v>1</v>
       </c>
       <c r="CV33" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="684" spans="91:91" x14ac:dyDescent="0.25">
@@ -6041,37 +6041,37 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -6085,43 +6085,43 @@
         <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -6150,13 +6150,13 @@
         <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>126</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>125</v>
@@ -6165,7 +6165,7 @@
         <v>125</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>125</v>
@@ -6176,55 +6176,55 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="K4" s="1">
         <v>5</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="K6" s="1">
         <v>99999</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="K7" s="1">
         <v>12</v>
@@ -6232,101 +6232,101 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="K11" s="1">
         <v>0.8</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J17" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J18" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -6352,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6363,10 +6363,10 @@
         <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6377,7 +6377,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>135</v>
@@ -6385,16 +6385,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -6420,7 +6420,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -6434,25 +6434,25 @@
         <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6481,7 +6481,7 @@
         <v>128</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>135</v>
@@ -6489,64 +6489,64 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E4" s="1">
         <v>4</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E5" s="1">
         <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E7" s="1">
         <v>2.25</v>
@@ -6555,18 +6555,18 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -6575,12 +6575,12 @@
         <v>2</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -6608,34 +6608,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -6643,34 +6643,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>104</v>
@@ -6719,10 +6719,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="K5" s="1">
         <v>60</v>
@@ -6733,10 +6733,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="K7" s="1">
         <v>60</v>
@@ -6744,17 +6744,17 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -6785,28 +6785,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>59</v>
@@ -6835,7 +6835,7 @@
         <v>128</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>128</v>
@@ -6871,28 +6871,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6900,28 +6900,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6955,28 +6955,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7B46E9-4DC6-4A6F-8608-31CCDB140BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9632CE2A-A45D-492D-8B70-210129180336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="622">
   <si>
     <t>Id</t>
   </si>
@@ -2198,6 +2198,10 @@
   </si>
   <si>
     <t>Skill_2_Loop</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2636,8 +2640,8 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
+      <c r="A4" s="5" t="s">
+        <v>621</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>

--- a/Excel/Test/Test.xlsx
+++ b/Excel/Test/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9632CE2A-A45D-492D-8B70-210129180336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF8648D-E7AA-4C8A-8E7D-144EBE0D92D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="693">
   <si>
     <t>Id</t>
   </si>
@@ -823,18 +823,12 @@
     <t>海水</t>
   </si>
   <si>
-    <t>萃蔓无敌</t>
-  </si>
-  <si>
     <t>潮起</t>
   </si>
   <si>
     <t>辅助</t>
   </si>
   <si>
-    <t>{"TexturePath":"Icon/otto.png","Alpha":0.5}</t>
-  </si>
-  <si>
     <t>enemy_1350_mgcshp_2</t>
   </si>
   <si>
@@ -1612,9 +1606,6 @@
     <t>普通法球</t>
   </si>
   <si>
-    <t>火墙附魔</t>
-  </si>
-  <si>
     <t>余火墙</t>
   </si>
   <si>
@@ -1954,9 +1945,6 @@
     <t>aglina_attack_01_trail</t>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":6,"SkillId":"CCB弹道索敌","CanBack":0,"ShowRange":0,"Color":"#EE3527","Homing":1,"LifeTime":30,"NavigationConstant":3,"HomingDelay":0.5,"MaxTurnRate":2160}</t>
-  </si>
-  <si>
     <t>真言天赋弹道</t>
   </si>
   <si>
@@ -1985,9 +1973,6 @@
   </si>
   <si>
     <t>milu_attack_01_trail</t>
-  </si>
-  <si>
-    <t>{"MoveHeight":0,"InitRadius":1.5,"Trigger":0.5,"LifeTime":5,"Alpha":0.25,"Color":"#f8c387"}</t>
   </si>
   <si>
     <t>thorns_attack_02_trail</t>
@@ -2182,10 +2167,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>agoat2_skill_03_buff_01</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>乌尔比安3爆炸</t>
   </si>
   <si>
@@ -2202,6 +2183,301 @@
   </si>
   <si>
     <t>CCB</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>干员</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>bsnake</t>
+  </si>
+  <si>
+    <t>无数次死去也不曾自乌萨斯土地上消失的古老意志。</t>
+  </si>
+  <si>
+    <t>Idle_A</t>
+  </si>
+  <si>
+    <t>Move_A</t>
+  </si>
+  <si>
+    <t>塔露拉</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉普攻</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通技能</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0#1,0</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>附加损伤</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Rate":0.1,"Base":"Damage","Element":"Fire"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉天赋</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署装置</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>42普攻击中</t>
+  </si>
+  <si>
+    <t>被动</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素爆发</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉火雨</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩箭</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>日冕重烈</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅自己</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Idle_B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉3A,塔露拉3B,塔露拉3加攻</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉3A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通Buff</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉3B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>42锁血特效</t>
+  </si>
+  <si>
+    <t>塔露拉3加攻</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"t":["AttackRate"]}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>火雨1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉元伤</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"DamageType":"Element"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>对buff切换伤害类型</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉普攻附加灼燃损伤</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉3附加灼燃损伤</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉元伤,塔露拉3附加灼燃损伤</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Rate":0.08,"Base":"Attack","Element":"Fire"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Muzzle</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉火球</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>amgoat_skill_02_trail</t>
+  </si>
+  <si>
+    <t>塔露拉火球AOE伤害</t>
+  </si>
+  <si>
+    <t>终点距离</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Fire":0.05}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球索敌</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>灼燃损伤减法抗</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>-灼燃损伤减法抗</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>火雨2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉普攻,塔露拉天赋</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓无敌,地板烫脚</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>地板烫脚</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t># 火墙附魔</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":6,"SkillId":"CCB弹道索敌","CanBack":0,"ShowRange":0,"Color":"#EE3527","Homing":1,"LifeTime":30,"NavigationConstant":3,"HomingDelay":0.5,"MaxTurnRate":2160}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"InitRadius":1.5,"Trigger":0.5,"LifeTime":5,"Alpha":0.25,"Color":"#f8c387"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面位</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉火球</t>
+  </si>
+  <si>
+    <t>{"Line":5, "扇形范围":288}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊2范围</t>
+  </si>
+  <si>
+    <t>42强力击击中</t>
+  </si>
+  <si>
+    <t>{"InitRadius": 1,"MaxRadius": 0.5,"RadiusExponentRate": -0.5,"DamageSkillId": "塔露拉火球AOE伤害","Trigger": 0.5,"SkillId": "火球索敌","Homing":1,"HomingDelay":0.5,"CollisionRadius": 0.3,"Alpha":0.25,"Color":"#f8c387"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Color":"#f13c22","Alpha":0.5}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Line":9,"StartPos":"背后方向"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reborn_1_End</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉3B特效</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉3二段特效</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"涨潮","召唤位置":"使用本技能索敌位置","持续":8,"ElementType":"Fire"}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>火雨1,火雨2,塔露拉火球AOE伤害,火球索敌,塔露拉3二段特效</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔露拉3二段特效结束</t>
+  </si>
+  <si>
+    <t>塔露拉3二段特效结束</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑蛇屏幕特效</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>screen_bsnake</t>
+  </si>
+  <si>
+    <t>1,-6,-0.5</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -2209,7 +2485,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2258,6 +2534,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2290,7 +2573,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2310,6 +2593,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2617,7 +2909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:B4"/>
+  <dimension ref="A2:B5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1" customWidth="1"/>
@@ -2641,10 +2933,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -2655,7 +2955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BX13"/>
+  <dimension ref="A1:BX16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
@@ -3307,13 +3607,13 @@
         <v>136</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="E5" s="2">
         <v>4231</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -3362,7 +3662,7 @@
         <v>137</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="AM5" s="3" t="s">
         <v>139</v>
@@ -3395,26 +3695,6 @@
         <f>"icon_"&amp;D5</f>
         <v>icon_clemnt</v>
       </c>
-      <c r="BH5" s="2" t="str">
-        <f>"half_"&amp;D5</f>
-        <v>half_clemnt</v>
-      </c>
-      <c r="BI5" s="2" t="str">
-        <f>D5</f>
-        <v>clemnt</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BK5" s="1">
-        <v>6</v>
-      </c>
-      <c r="BL5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="BQ5" s="1" t="s">
         <v>148</v>
       </c>
@@ -3439,7 +3719,7 @@
         <v>152</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="AM6" s="3"/>
     </row>
@@ -3554,7 +3834,7 @@
         <v>164</v>
       </c>
       <c r="G9" s="1">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="J9" s="1">
         <v>2</v>
@@ -3601,11 +3881,8 @@
       <c r="AK9" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AL9" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="AM9" s="1" t="s">
-        <v>167</v>
+      <c r="AL9" s="5" t="s">
+        <v>670</v>
       </c>
       <c r="AO9" s="2"/>
       <c r="AQ9" s="1" t="s">
@@ -3624,20 +3901,20 @@
         <v>0.25</v>
       </c>
       <c r="BE9" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="BO9" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
+      </c>
+      <c r="BO9" s="5" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="10" spans="1:76" x14ac:dyDescent="0.25">
       <c r="E10" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>136</v>
@@ -3710,7 +3987,7 @@
         <v>0.25</v>
       </c>
       <c r="BG11" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="BM11" s="2" t="s">
         <v>159</v>
@@ -3736,7 +4013,7 @@
     </row>
     <row r="12" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>136</v>
@@ -3809,7 +4086,7 @@
         <v>0.25</v>
       </c>
       <c r="BG12" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="BM12" s="2" t="s">
         <v>159</v>
@@ -3835,7 +4112,7 @@
     </row>
     <row r="13" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>136</v>
@@ -3908,7 +4185,7 @@
         <v>0.25</v>
       </c>
       <c r="BG13" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BM13" s="2" t="s">
         <v>159</v>
@@ -3929,6 +4206,150 @@
         <v>150</v>
       </c>
       <c r="BX13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1515</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <f t="shared" ref="F16" si="1">"enemy_"&amp;E16&amp;"_"&amp;D16</f>
+        <v>enemy_1515_bsnake</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>2</v>
+      </c>
+      <c r="K16" s="2">
+        <v>90</v>
+      </c>
+      <c r="L16" s="2">
+        <v>2910</v>
+      </c>
+      <c r="N16" s="2">
+        <v>965</v>
+      </c>
+      <c r="P16" s="2">
+        <v>425</v>
+      </c>
+      <c r="R16" s="2">
+        <v>10</v>
+      </c>
+      <c r="T16" s="2">
+        <v>21</v>
+      </c>
+      <c r="W16" s="2">
+        <v>70</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="AK16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL16" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="AM16" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="AN16" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ16" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="AR16" s="2">
+        <v>2</v>
+      </c>
+      <c r="AS16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AZ16" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="BE16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BG16" s="2" t="str">
+        <f t="shared" ref="BG16" si="2">"enemy_"&amp;E16&amp;"_"&amp;D16</f>
+        <v>enemy_1515_bsnake</v>
+      </c>
+      <c r="BH16" s="2" t="str">
+        <f>"half_"&amp;D5</f>
+        <v>half_clemnt</v>
+      </c>
+      <c r="BI16" s="2" t="str">
+        <f>D5</f>
+        <v>clemnt</v>
+      </c>
+      <c r="BJ16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BK16" s="1">
+        <v>6</v>
+      </c>
+      <c r="BL16" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BM16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="BN16" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="BP16" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="BQ16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BR16" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="BS16" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="BT16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BX16" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3942,7 +4363,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ704"/>
+  <dimension ref="A1:DJ706"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" style="1" customWidth="1"/>
@@ -4032,337 +4453,337 @@
   <sheetData>
     <row r="1" spans="1:114" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="BJ1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="CT1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="CS1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="DB1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="DA1" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="DJ1" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:114" x14ac:dyDescent="0.25">
@@ -4376,334 +4797,334 @@
         <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="BO2" s="1" t="s">
         <v>86</v>
       </c>
       <c r="BP2" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="BR2" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BS2" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BT2" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="BT2" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="BU2" s="1" t="s">
         <v>102</v>
       </c>
       <c r="BV2" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="BW2" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="BX2" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BY2" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="BX2" s="1" t="s">
+      <c r="BZ2" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="CA2" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="CE2" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="CH2" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="CK2" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="CL2" s="1" t="s">
+      <c r="CN2" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="CM2" s="1" t="s">
+      <c r="CO2" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="CN2" s="1" t="s">
+      <c r="CP2" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="CP2" s="1" t="s">
+      <c r="CR2" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="CQ2" s="1" t="s">
+      <c r="CS2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="CR2" s="1" t="s">
+      <c r="CT2" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="CS2" s="1" t="s">
+      <c r="CU2" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="CT2" s="1" t="s">
+      <c r="CV2" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="CU2" s="1" t="s">
+      <c r="CW2" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="CV2" s="1" t="s">
+      <c r="CX2" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="CW2" s="1" t="s">
+      <c r="CY2" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="CX2" s="1" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="CY2" s="1" t="s">
+      <c r="DA2" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="CZ2" s="1" t="s">
+      <c r="DB2" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="DA2" s="1" t="s">
+      <c r="DC2" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="DB2" s="1" t="s">
+      <c r="DD2" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="DC2" s="1" t="s">
+      <c r="DE2" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="DD2" s="1" t="s">
+      <c r="DF2" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="DE2" s="1" t="s">
+      <c r="DG2" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="DF2" s="1" t="s">
+      <c r="DH2" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="DG2" s="1" t="s">
+      <c r="DI2" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="DH2" s="1" t="s">
+      <c r="DJ2" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="DI2" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="DJ2" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:114" x14ac:dyDescent="0.25">
@@ -4732,13 +5153,13 @@
         <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>128</v>
@@ -4801,7 +5222,7 @@
         <v>125</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AH3" s="1" t="s">
         <v>125</v>
@@ -4825,10 +5246,10 @@
         <v>125</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4840,7 +5261,7 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AU3" s="1" t="s">
         <v>125</v>
@@ -4852,7 +5273,7 @@
         <v>125</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AY3" s="1" t="s">
         <v>125</v>
@@ -4882,7 +5303,7 @@
         <v>125</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="BI3" s="1" t="s">
         <v>125</v>
@@ -4909,10 +5330,10 @@
         <v>129</v>
       </c>
       <c r="BQ3" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="BR3" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="BS3" s="1" t="s">
         <v>126</v>
@@ -4933,13 +5354,13 @@
         <v>128</v>
       </c>
       <c r="BY3" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="BZ3" s="1" t="s">
         <v>125</v>
       </c>
       <c r="CA3" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="CB3" s="1" t="s">
         <v>130</v>
@@ -4948,7 +5369,7 @@
         <v>125</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="CE3" s="1" t="s">
         <v>130</v>
@@ -4960,19 +5381,19 @@
         <v>130</v>
       </c>
       <c r="CH3" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="CI3" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="CJ3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="CK3" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="CL3" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="CM3" s="1" t="s">
         <v>135</v>
@@ -4993,7 +5414,7 @@
         <v>134</v>
       </c>
       <c r="CS3" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="CT3" s="1" t="s">
         <v>134</v>
@@ -5005,28 +5426,28 @@
         <v>135</v>
       </c>
       <c r="CW3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="CX3" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="CY3" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="CZ3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="DC3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="DE3" s="1" t="s">
         <v>125</v>
@@ -5049,7 +5470,7 @@
     </row>
     <row r="4" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:114" x14ac:dyDescent="0.25">
@@ -5057,13 +5478,13 @@
         <v>138</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="AC6" s="1">
         <v>2</v>
@@ -5072,13 +5493,13 @@
         <v>1</v>
       </c>
       <c r="AO6" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="AT6" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AX6" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="AT6" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="AX6" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="AZ6" s="1">
         <v>1</v>
@@ -5093,37 +5514,37 @@
         <v>0.25</v>
       </c>
       <c r="BP6" s="1" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="BQ6" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="CB6" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="CH6" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="CI6" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="CB6" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="CH6" s="1" t="s">
+      <c r="CJ6" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="CI6" s="1" t="s">
+      <c r="CK6" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="CJ6" s="1" t="s">
+      <c r="CO6" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="CK6" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="CO6" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="CS6" s="1">
         <v>12</v>
       </c>
       <c r="CV6" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="CZ6" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="DE6" s="1">
         <v>1</v>
@@ -5137,19 +5558,19 @@
     </row>
     <row r="7" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="AC7" s="1">
         <v>2</v>
@@ -5158,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AV7" s="1">
         <v>16</v>
@@ -5167,30 +5588,30 @@
         <v>99</v>
       </c>
       <c r="CI7" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:114" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:114" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AZ8" s="1">
         <v>0</v>
@@ -5202,30 +5623,30 @@
         <v>1</v>
       </c>
       <c r="CM8" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="CZ8" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="AC10" s="1">
         <v>1</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="BD10" s="1">
         <v>1</v>
@@ -5243,36 +5664,36 @@
         <v>1</v>
       </c>
       <c r="BY10" s="6" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="CO10" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AV12" s="1">
         <v>8</v>
       </c>
       <c r="AX12" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AZ12" s="1">
         <v>2.5</v>
@@ -5293,51 +5714,51 @@
         <v>1</v>
       </c>
       <c r="BY12" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="CB12" s="1" t="s">
         <v>62</v>
       </c>
       <c r="CH12" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="CI12" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="CJ12" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="CK12" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="CO12" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="CV12" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="CJ12" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="CK12" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="CO12" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="CV12" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="CZ12" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AC13" s="1">
         <v>1</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="BD13" s="1">
         <v>1</v>
@@ -5355,10 +5776,10 @@
         <v>1</v>
       </c>
       <c r="BY13" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="CO13" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="CP13" s="1">
         <v>200</v>
@@ -5372,22 +5793,22 @@
     </row>
     <row r="14" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AC14" s="1">
         <v>1</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="BD14" s="1">
         <v>1</v>
@@ -5405,39 +5826,39 @@
         <v>1</v>
       </c>
       <c r="BY14" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="CO14" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="CV14" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AC16" s="1">
         <v>2</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AR16" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AV16" s="1">
         <v>8</v>
       </c>
       <c r="AX16" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AZ16" s="1">
         <v>1.5</v>
@@ -5449,10 +5870,10 @@
         <v>6</v>
       </c>
       <c r="CI16" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="CO16" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="CP16" s="1">
         <v>-50</v>
@@ -5464,24 +5885,24 @@
         <v>3</v>
       </c>
       <c r="CV16" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5493,33 +5914,33 @@
         <v>1</v>
       </c>
       <c r="CV17" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AC18" s="1">
         <v>2</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AR18" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AV18" s="1">
         <v>3.5</v>
       </c>
       <c r="AX18" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AZ18" s="1">
         <v>1</v>
@@ -5531,25 +5952,25 @@
         <v>62</v>
       </c>
       <c r="CH18" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="CI18" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="CJ18" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="CO18" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="CP18" s="1">
         <v>-0.8</v>
       </c>
       <c r="CV18" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="CZ18" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:113" x14ac:dyDescent="0.25">
@@ -5557,19 +5978,19 @@
         <v>157</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
@@ -5587,10 +6008,10 @@
         <v>1</v>
       </c>
       <c r="BY19" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="CO19" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="CP19" s="1">
         <v>100</v>
@@ -5601,16 +6022,16 @@
     </row>
     <row r="20" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AC20" s="1">
         <v>1</v>
@@ -5619,10 +6040,10 @@
         <v>1</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AX20" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AZ20" s="1">
         <v>0.05</v>
@@ -5637,7 +6058,7 @@
         <v>0.5</v>
       </c>
       <c r="CZ20" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="DE20" s="1">
         <v>1</v>
@@ -5651,16 +6072,16 @@
     </row>
     <row r="22" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="X22" s="1">
         <v>1</v>
@@ -5681,24 +6102,24 @@
         <v>1</v>
       </c>
       <c r="BY22" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="CV22" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="L23" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AC23" s="1">
         <v>7</v>
@@ -5707,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AN23" s="1">
         <v>1</v>
@@ -5727,16 +6148,16 @@
     </row>
     <row r="25" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="X25" s="1">
         <v>1</v>
@@ -5754,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="AX25" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AZ25" s="1">
         <v>1.5</v>
@@ -5769,7 +6190,7 @@
         <v>0.04</v>
       </c>
       <c r="BP25" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="BT25" s="1">
         <v>2.5</v>
@@ -5784,54 +6205,54 @@
         <v>1</v>
       </c>
       <c r="BY25" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="CB25" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="CF25" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG25" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="CH25" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="CI25" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="CJ25" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="CB25" s="1" t="s">
+      <c r="CK25" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="CV25" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="CF25" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="CG25" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="CH25" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="CI25" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="CJ25" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="CK25" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="CV25" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="26" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="AC26" s="1">
         <v>1</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="BD26" s="1">
         <v>1</v>
       </c>
       <c r="CO26" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="CS26" s="1">
         <v>3</v>
@@ -5842,22 +6263,22 @@
         <v>139</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="BT28" s="1">
         <v>2.5</v>
@@ -5872,143 +6293,599 @@
         <v>1</v>
       </c>
       <c r="BY28" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="31" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="BD31" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV31" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="BD31" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV31" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="BD32" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV32" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="33" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="BD33" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV33" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="BD32" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV32" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="33" spans="1:100" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="BD33" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV33" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="684" spans="91:91" x14ac:dyDescent="0.25">
-      <c r="CM684" s="1">
+    </row>
+    <row r="35" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AC35" s="1">
+        <v>2</v>
+      </c>
+      <c r="AO35" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="AT35" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="AX35" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="AZ35" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD35" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB35" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="CH35" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="CK35" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="CM35" s="6"/>
+      <c r="CZ35" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="37" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="AC37" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO37" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="AV37" s="1">
+        <v>99</v>
+      </c>
+      <c r="AX37" s="6"/>
+      <c r="BS37" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="CV37" s="6" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="38" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="L38" s="6"/>
+      <c r="AC38" s="1">
+        <v>2</v>
+      </c>
+      <c r="AO38" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="AT38" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="AX38" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="AZ38" s="1">
         <v>0.15</v>
+      </c>
+      <c r="BB38" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD38" s="1">
+        <v>99</v>
+      </c>
+      <c r="BS38" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="CV38" s="6"/>
+      <c r="DE38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="G40" s="1">
+        <v>3</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="AC40" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="AT40" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="BD40" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO40" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="BT40" s="1">
+        <v>36</v>
+      </c>
+      <c r="BV40" s="1">
+        <v>35</v>
+      </c>
+      <c r="BW40" s="1">
+        <v>40</v>
+      </c>
+      <c r="BX40" s="1">
+        <v>1</v>
+      </c>
+      <c r="BY40" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="CF40" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="CO40" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="CR40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX41" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="AZ41" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD41" s="1">
+        <v>99</v>
+      </c>
+      <c r="BJ41" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="BK41" s="1">
+        <v>1</v>
+      </c>
+      <c r="BL41" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="BS41" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="BT41" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="BV41" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW41" s="1">
+        <v>1</v>
+      </c>
+      <c r="BX41" s="1">
+        <v>1</v>
+      </c>
+      <c r="BY41" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="CI41" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="CJ41" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="CK41" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="CV41" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="CZ41" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="DE41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX42" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="AZ42" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD42" s="1">
+        <v>99</v>
+      </c>
+      <c r="BJ42" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="BK42" s="1">
+        <v>1</v>
+      </c>
+      <c r="BL42" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="BS42" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="BT42" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="BV42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW42" s="1">
+        <v>1</v>
+      </c>
+      <c r="BX42" s="1">
+        <v>1</v>
+      </c>
+      <c r="BY42" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="CI42" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="CJ42" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="CK42" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="CV42" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="CZ42" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="DE42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="BO43" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="CO43" s="6" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="44" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="AC44" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="CN44" s="6" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="45" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>2</v>
+      </c>
+      <c r="AO45" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="AX45" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="AZ45" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BD45" s="1">
+        <v>99</v>
+      </c>
+      <c r="CM45" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="CZ45" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="47" spans="1:109" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="AC47" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD47" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO47" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="AR47" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="AV47" s="1">
+        <v>8</v>
+      </c>
+      <c r="DE47" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="686" spans="91:91" x14ac:dyDescent="0.25">
       <c r="CM686" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="688" spans="91:91" x14ac:dyDescent="0.25">
+      <c r="CM688" s="1">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="687" spans="91:91" x14ac:dyDescent="0.25">
-      <c r="CM687" s="1">
-        <v>0.1</v>
       </c>
     </row>
     <row r="689" spans="91:91" x14ac:dyDescent="0.25">
       <c r="CM689" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="691" spans="91:91" x14ac:dyDescent="0.25">
+      <c r="CM691" s="1">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="696" spans="91:91" x14ac:dyDescent="0.25">
-      <c r="CM696" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="698" spans="91:91" x14ac:dyDescent="0.25">
       <c r="CM698" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700" spans="91:91" x14ac:dyDescent="0.25">
+      <c r="CM700" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="699" spans="91:91" x14ac:dyDescent="0.25">
-      <c r="CM699" s="1">
+    <row r="701" spans="91:91" x14ac:dyDescent="0.25">
+      <c r="CM701" s="1">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="702" spans="91:91" x14ac:dyDescent="0.25">
-      <c r="CM702" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="703" spans="91:91" x14ac:dyDescent="0.25">
-      <c r="CM703" s="1">
-        <v>0.66700000000000004</v>
       </c>
     </row>
     <row r="704" spans="91:91" x14ac:dyDescent="0.25">
       <c r="CM704" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="705" spans="91:91" x14ac:dyDescent="0.25">
+      <c r="CM705" s="1">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="706" spans="91:91" x14ac:dyDescent="0.25">
+      <c r="CM706" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -6022,7 +6899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -6045,37 +6922,37 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -6089,43 +6966,43 @@
         <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -6154,13 +7031,13 @@
         <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>126</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>125</v>
@@ -6169,7 +7046,7 @@
         <v>125</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>125</v>
@@ -6180,55 +7057,55 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="K4" s="1">
         <v>5</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K6" s="1">
         <v>99999</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="K7" s="1">
         <v>12</v>
@@ -6236,69 +7113,69 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="K11" s="1">
         <v>0.8</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -6306,31 +7183,85 @@
         <v>162</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="J17" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J18" s="3" t="s">
-        <v>520</v>
+        <v>608</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="K18" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="K19" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="1">
+        <v>36</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="K21" s="1">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -6342,7 +7273,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
@@ -6356,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6367,10 +7298,10 @@
         <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6381,7 +7312,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>135</v>
@@ -6389,16 +7320,52 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -6424,7 +7391,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -6438,25 +7405,25 @@
         <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6485,7 +7452,7 @@
         <v>128</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>135</v>
@@ -6493,64 +7460,64 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E4" s="1">
         <v>4</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>543</v>
+      <c r="J4" s="5" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E5" s="1">
         <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E7" s="1">
         <v>2.25</v>
@@ -6559,18 +7526,18 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -6578,13 +7545,30 @@
       <c r="F8" s="1">
         <v>2</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>554</v>
+      <c r="J8" s="5" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -6612,34 +7596,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -6647,34 +7631,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>104</v>
@@ -6722,25 +7706,25 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>520</v>
+      <c r="A5" s="9" t="s">
+        <v>690</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>616</v>
+        <v>691</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>692</v>
       </c>
       <c r="K5" s="1">
-        <v>60</v>
-      </c>
-      <c r="L5" s="1">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="K7" s="1">
         <v>60</v>
@@ -6748,17 +7732,17 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -6789,28 +7773,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>59</v>
@@ -6839,7 +7823,7 @@
         <v>128</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>128</v>
@@ -6875,28 +7859,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6904,28 +7888,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6959,28 +7943,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
   </sheetData>
